--- a/Avaliacao_Pastoral_MCASD_2026.xlsx
+++ b/Avaliacao_Pastoral_MCASD_2026.xlsx
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -185,6 +185,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -270,7 +279,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
+    <ext cx="476250" cy="476250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -278,31 +287,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>14</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="619125" cy="400050"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -608,57 +592,57 @@
   <dimension ref="A1:N106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>MATRIZ CONSOLIDADA DE AVALIAÇÃO PASTORAL — MCASD 2026</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Sistema de Avaliação Pastoral | União Sudoeste de Angola — Missão Centro | Escala: 1=Deficiente (D) | 2=Regular (R) | 3=Bom (B) | 4=Muito Bom (MB) | 5=Excelente (E)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
+          <t>União Sudoeste de Angola — Missão Centro | Escala: 1=Deficiente | 2=Regular | 3=Bom | 4=Muito Bom | 5=Excelente</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>👤 UTILIZADOR ATIVO: Pr. Valentino Canguele | Host: macbooks-MBP (root)</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>🔄 SINCRONIZAR SUPABASE CLOUD</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="20" customHeight="1">
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>🪪 LICENÇA: 2026-MCASD-PASTOR-001 | IP: 192.168.0.40 | Data/Hora: 20/08/2026 13:11:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="12" customHeight="1"/>
-    <row r="6" ht="42" customHeight="1">
+          <t>🪪 LICENÇA: 2026-MCASD-PASTOR-001 | IP: 192.168.0.40 | Data/Hora: 20/08/2026 13:43:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="10" customHeight="1"/>
+    <row r="6" ht="38" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Nº</t>
@@ -737,7 +721,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="7" t="n">
         <v>1</v>
       </c>
@@ -793,7 +777,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="11" t="n">
         <v>2</v>
       </c>
@@ -849,7 +833,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="7" t="n">
         <v>3</v>
       </c>
@@ -905,7 +889,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>4</v>
       </c>
@@ -961,7 +945,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="7" t="n">
         <v>5</v>
       </c>
@@ -1017,7 +1001,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="11" t="n">
         <v>6</v>
       </c>
@@ -1073,7 +1057,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="7" t="n">
         <v>7</v>
       </c>
@@ -1129,7 +1113,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>8</v>
       </c>
@@ -1185,7 +1169,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="7" t="n">
         <v>9</v>
       </c>
@@ -1241,7 +1225,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1">
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="11" t="n">
         <v>10</v>
       </c>
@@ -1297,7 +1281,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="7" t="n">
         <v>11</v>
       </c>
@@ -1353,7 +1337,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="11" t="n">
         <v>12</v>
       </c>
@@ -1409,7 +1393,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="7" t="n">
         <v>13</v>
       </c>
@@ -1465,7 +1449,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="11" t="n">
         <v>14</v>
       </c>
@@ -1521,7 +1505,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="26" customHeight="1">
+    <row r="21" ht="24" customHeight="1">
       <c r="A21" s="7" t="n">
         <v>15</v>
       </c>
@@ -1577,7 +1561,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
+    <row r="22" ht="24" customHeight="1">
       <c r="A22" s="11" t="n">
         <v>16</v>
       </c>
@@ -1633,7 +1617,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="26" customHeight="1">
+    <row r="23" ht="24" customHeight="1">
       <c r="A23" s="7" t="n">
         <v>17</v>
       </c>
@@ -1689,7 +1673,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="26" customHeight="1">
+    <row r="24" ht="24" customHeight="1">
       <c r="A24" s="11" t="n">
         <v>18</v>
       </c>
@@ -1745,7 +1729,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="26" customHeight="1">
+    <row r="25" ht="24" customHeight="1">
       <c r="A25" s="7" t="n">
         <v>19</v>
       </c>
@@ -1801,7 +1785,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="26" customHeight="1">
+    <row r="26" ht="24" customHeight="1">
       <c r="A26" s="11" t="n">
         <v>20</v>
       </c>
@@ -1857,7 +1841,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="26" customHeight="1">
+    <row r="27" ht="24" customHeight="1">
       <c r="A27" s="7" t="n">
         <v>21</v>
       </c>
@@ -1913,7 +1897,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="26" customHeight="1">
+    <row r="28" ht="24" customHeight="1">
       <c r="A28" s="11" t="n">
         <v>22</v>
       </c>
@@ -1969,7 +1953,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="26" customHeight="1">
+    <row r="29" ht="24" customHeight="1">
       <c r="A29" s="7" t="n">
         <v>23</v>
       </c>
@@ -2025,7 +2009,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
+    <row r="30" ht="24" customHeight="1">
       <c r="A30" s="11" t="n">
         <v>24</v>
       </c>
@@ -2081,7 +2065,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="26" customHeight="1">
+    <row r="31" ht="24" customHeight="1">
       <c r="A31" s="7" t="n">
         <v>25</v>
       </c>
@@ -2137,7 +2121,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="26" customHeight="1">
+    <row r="32" ht="24" customHeight="1">
       <c r="A32" s="11" t="n">
         <v>26</v>
       </c>
@@ -2193,7 +2177,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="26" customHeight="1">
+    <row r="33" ht="24" customHeight="1">
       <c r="A33" s="7" t="n">
         <v>27</v>
       </c>
@@ -2249,7 +2233,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="26" customHeight="1">
+    <row r="34" ht="24" customHeight="1">
       <c r="A34" s="11" t="n">
         <v>28</v>
       </c>
@@ -2305,7 +2289,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="26" customHeight="1">
+    <row r="35" ht="24" customHeight="1">
       <c r="A35" s="7" t="n">
         <v>29</v>
       </c>
@@ -2361,7 +2345,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="26" customHeight="1">
+    <row r="36" ht="24" customHeight="1">
       <c r="A36" s="11" t="n">
         <v>30</v>
       </c>
@@ -2417,7 +2401,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="26" customHeight="1">
+    <row r="37" ht="24" customHeight="1">
       <c r="A37" s="7" t="n">
         <v>31</v>
       </c>
@@ -2473,7 +2457,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="26" customHeight="1">
+    <row r="38" ht="24" customHeight="1">
       <c r="A38" s="11" t="n">
         <v>32</v>
       </c>
@@ -2529,7 +2513,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="26" customHeight="1">
+    <row r="39" ht="24" customHeight="1">
       <c r="A39" s="7" t="n">
         <v>33</v>
       </c>
@@ -2585,7 +2569,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="26" customHeight="1">
+    <row r="40" ht="24" customHeight="1">
       <c r="A40" s="11" t="n">
         <v>34</v>
       </c>
@@ -2641,7 +2625,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="26" customHeight="1">
+    <row r="41" ht="24" customHeight="1">
       <c r="A41" s="7" t="n">
         <v>35</v>
       </c>
@@ -2697,7 +2681,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="26" customHeight="1">
+    <row r="42" ht="24" customHeight="1">
       <c r="A42" s="11" t="n">
         <v>36</v>
       </c>
@@ -2753,7 +2737,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="26" customHeight="1">
+    <row r="43" ht="24" customHeight="1">
       <c r="A43" s="7" t="n">
         <v>37</v>
       </c>
@@ -2809,7 +2793,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="26" customHeight="1">
+    <row r="44" ht="24" customHeight="1">
       <c r="A44" s="11" t="n">
         <v>38</v>
       </c>
@@ -2865,7 +2849,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="26" customHeight="1">
+    <row r="45" ht="24" customHeight="1">
       <c r="A45" s="7" t="n">
         <v>39</v>
       </c>
@@ -2921,7 +2905,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="26" customHeight="1">
+    <row r="46" ht="24" customHeight="1">
       <c r="A46" s="11" t="n">
         <v>40</v>
       </c>
@@ -2977,7 +2961,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="26" customHeight="1">
+    <row r="47" ht="24" customHeight="1">
       <c r="A47" s="7" t="n">
         <v>41</v>
       </c>
@@ -3033,7 +3017,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="26" customHeight="1">
+    <row r="48" ht="24" customHeight="1">
       <c r="A48" s="11" t="n">
         <v>42</v>
       </c>
@@ -3089,7 +3073,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="26" customHeight="1">
+    <row r="49" ht="24" customHeight="1">
       <c r="A49" s="7" t="n">
         <v>43</v>
       </c>
@@ -3145,7 +3129,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="26" customHeight="1">
+    <row r="50" ht="24" customHeight="1">
       <c r="A50" s="11" t="n">
         <v>44</v>
       </c>
@@ -3201,7 +3185,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="26" customHeight="1">
+    <row r="51" ht="24" customHeight="1">
       <c r="A51" s="7" t="n">
         <v>45</v>
       </c>
@@ -3257,7 +3241,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="26" customHeight="1">
+    <row r="52" ht="24" customHeight="1">
       <c r="A52" s="11" t="n">
         <v>46</v>
       </c>
@@ -3313,7 +3297,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="26" customHeight="1">
+    <row r="53" ht="24" customHeight="1">
       <c r="A53" s="7" t="n">
         <v>47</v>
       </c>
@@ -3369,7 +3353,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="26" customHeight="1">
+    <row r="54" ht="24" customHeight="1">
       <c r="A54" s="11" t="n">
         <v>48</v>
       </c>
@@ -3425,7 +3409,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="26" customHeight="1">
+    <row r="55" ht="24" customHeight="1">
       <c r="A55" s="7" t="n">
         <v>49</v>
       </c>
@@ -3481,7 +3465,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="26" customHeight="1">
+    <row r="56" ht="24" customHeight="1">
       <c r="A56" s="11" t="n">
         <v>50</v>
       </c>
@@ -3537,7 +3521,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="26" customHeight="1">
+    <row r="57" ht="24" customHeight="1">
       <c r="A57" s="7" t="n">
         <v>51</v>
       </c>
@@ -3593,7 +3577,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="26" customHeight="1">
+    <row r="58" ht="24" customHeight="1">
       <c r="A58" s="11" t="n">
         <v>52</v>
       </c>
@@ -3649,7 +3633,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="26" customHeight="1">
+    <row r="59" ht="24" customHeight="1">
       <c r="A59" s="7" t="n">
         <v>53</v>
       </c>
@@ -3705,7 +3689,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="26" customHeight="1">
+    <row r="60" ht="24" customHeight="1">
       <c r="A60" s="11" t="n">
         <v>54</v>
       </c>
@@ -3761,7 +3745,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="26" customHeight="1">
+    <row r="61" ht="24" customHeight="1">
       <c r="A61" s="7" t="n">
         <v>55</v>
       </c>
@@ -3817,7 +3801,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="26" customHeight="1">
+    <row r="62" ht="24" customHeight="1">
       <c r="A62" s="11" t="n">
         <v>56</v>
       </c>
@@ -3873,7 +3857,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="26" customHeight="1">
+    <row r="63" ht="24" customHeight="1">
       <c r="A63" s="7" t="n">
         <v>57</v>
       </c>
@@ -3929,7 +3913,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="26" customHeight="1">
+    <row r="64" ht="24" customHeight="1">
       <c r="A64" s="11" t="n">
         <v>58</v>
       </c>
@@ -3985,7 +3969,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="26" customHeight="1">
+    <row r="65" ht="24" customHeight="1">
       <c r="A65" s="7" t="n">
         <v>59</v>
       </c>
@@ -4041,7 +4025,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="26" customHeight="1">
+    <row r="66" ht="24" customHeight="1">
       <c r="A66" s="11" t="n">
         <v>60</v>
       </c>
@@ -4097,7 +4081,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="26" customHeight="1">
+    <row r="67" ht="24" customHeight="1">
       <c r="A67" s="7" t="n">
         <v>61</v>
       </c>
@@ -4153,7 +4137,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="26" customHeight="1">
+    <row r="68" ht="24" customHeight="1">
       <c r="A68" s="11" t="n">
         <v>62</v>
       </c>
@@ -4209,7 +4193,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="26" customHeight="1">
+    <row r="69" ht="24" customHeight="1">
       <c r="A69" s="7" t="n">
         <v>63</v>
       </c>
@@ -4265,7 +4249,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="26" customHeight="1">
+    <row r="70" ht="24" customHeight="1">
       <c r="A70" s="11" t="n">
         <v>64</v>
       </c>
@@ -4321,7 +4305,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="26" customHeight="1">
+    <row r="71" ht="24" customHeight="1">
       <c r="A71" s="7" t="n">
         <v>65</v>
       </c>
@@ -4377,7 +4361,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="26" customHeight="1">
+    <row r="72" ht="24" customHeight="1">
       <c r="A72" s="11" t="n">
         <v>66</v>
       </c>
@@ -4433,7 +4417,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="26" customHeight="1">
+    <row r="73" ht="24" customHeight="1">
       <c r="A73" s="7" t="n">
         <v>67</v>
       </c>
@@ -4489,7 +4473,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="26" customHeight="1">
+    <row r="74" ht="24" customHeight="1">
       <c r="A74" s="11" t="n">
         <v>68</v>
       </c>
@@ -4545,7 +4529,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="26" customHeight="1">
+    <row r="75" ht="24" customHeight="1">
       <c r="A75" s="7" t="n">
         <v>69</v>
       </c>
@@ -4601,7 +4585,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="26" customHeight="1">
+    <row r="76" ht="24" customHeight="1">
       <c r="A76" s="11" t="n">
         <v>70</v>
       </c>
@@ -4657,7 +4641,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="26" customHeight="1">
+    <row r="77" ht="24" customHeight="1">
       <c r="A77" s="7" t="n">
         <v>71</v>
       </c>
@@ -4713,7 +4697,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="26" customHeight="1">
+    <row r="78" ht="24" customHeight="1">
       <c r="A78" s="11" t="n">
         <v>72</v>
       </c>
@@ -4769,7 +4753,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="26" customHeight="1">
+    <row r="79" ht="24" customHeight="1">
       <c r="A79" s="7" t="n">
         <v>73</v>
       </c>
@@ -4825,7 +4809,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="26" customHeight="1">
+    <row r="80" ht="24" customHeight="1">
       <c r="A80" s="11" t="n">
         <v>74</v>
       </c>
@@ -4881,7 +4865,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="26" customHeight="1">
+    <row r="81" ht="24" customHeight="1">
       <c r="A81" s="7" t="n">
         <v>75</v>
       </c>
@@ -4937,7 +4921,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="26" customHeight="1">
+    <row r="82" ht="24" customHeight="1">
       <c r="A82" s="11" t="n">
         <v>76</v>
       </c>
@@ -4993,7 +4977,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="26" customHeight="1">
+    <row r="83" ht="24" customHeight="1">
       <c r="A83" s="7" t="n">
         <v>77</v>
       </c>
@@ -5049,7 +5033,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="26" customHeight="1">
+    <row r="84" ht="24" customHeight="1">
       <c r="A84" s="11" t="n">
         <v>78</v>
       </c>
@@ -5105,7 +5089,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="26" customHeight="1">
+    <row r="85" ht="24" customHeight="1">
       <c r="A85" s="7" t="n">
         <v>79</v>
       </c>
@@ -5161,7 +5145,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="26" customHeight="1">
+    <row r="86" ht="24" customHeight="1">
       <c r="A86" s="11" t="n">
         <v>80</v>
       </c>
@@ -5217,7 +5201,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="26" customHeight="1">
+    <row r="87" ht="24" customHeight="1">
       <c r="A87" s="7" t="n">
         <v>81</v>
       </c>
@@ -5273,7 +5257,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="26" customHeight="1">
+    <row r="88" ht="24" customHeight="1">
       <c r="A88" s="11" t="n">
         <v>82</v>
       </c>
@@ -5329,7 +5313,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="26" customHeight="1">
+    <row r="89" ht="24" customHeight="1">
       <c r="A89" s="7" t="n">
         <v>83</v>
       </c>
@@ -5385,7 +5369,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="26" customHeight="1">
+    <row r="90" ht="24" customHeight="1">
       <c r="A90" s="11" t="n">
         <v>84</v>
       </c>
@@ -5441,7 +5425,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="26" customHeight="1">
+    <row r="91" ht="24" customHeight="1">
       <c r="A91" s="7" t="n">
         <v>85</v>
       </c>
@@ -5497,7 +5481,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="26" customHeight="1">
+    <row r="92" ht="24" customHeight="1">
       <c r="A92" s="11" t="n">
         <v>86</v>
       </c>
@@ -5553,7 +5537,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="26" customHeight="1">
+    <row r="93" ht="24" customHeight="1">
       <c r="A93" s="7" t="n">
         <v>87</v>
       </c>
@@ -5609,7 +5593,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="26" customHeight="1">
+    <row r="94" ht="24" customHeight="1">
       <c r="A94" s="11" t="n">
         <v>88</v>
       </c>
@@ -5665,7 +5649,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="26" customHeight="1">
+    <row r="95" ht="24" customHeight="1">
       <c r="A95" s="7" t="n">
         <v>89</v>
       </c>
@@ -5721,7 +5705,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="26" customHeight="1">
+    <row r="96" ht="24" customHeight="1">
       <c r="A96" s="11" t="n">
         <v>90</v>
       </c>
@@ -5777,7 +5761,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="26" customHeight="1">
+    <row r="97" ht="24" customHeight="1">
       <c r="A97" s="7" t="n">
         <v>91</v>
       </c>
@@ -5833,7 +5817,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="26" customHeight="1">
+    <row r="98" ht="24" customHeight="1">
       <c r="A98" s="11" t="n">
         <v>92</v>
       </c>
@@ -5889,7 +5873,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="26" customHeight="1">
+    <row r="99" ht="24" customHeight="1">
       <c r="A99" s="7" t="n">
         <v>93</v>
       </c>
@@ -5945,7 +5929,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="26" customHeight="1">
+    <row r="100" ht="24" customHeight="1">
       <c r="A100" s="11" t="n">
         <v>94</v>
       </c>
@@ -6001,7 +5985,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="26" customHeight="1">
+    <row r="101" ht="24" customHeight="1">
       <c r="A101" s="7" t="n">
         <v>95</v>
       </c>
@@ -6057,7 +6041,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="26" customHeight="1">
+    <row r="102" ht="24" customHeight="1">
       <c r="A102" s="11" t="n">
         <v>96</v>
       </c>
@@ -6113,7 +6097,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="26" customHeight="1">
+    <row r="103" ht="24" customHeight="1">
       <c r="A103" s="7" t="n">
         <v>97</v>
       </c>
@@ -6169,7 +6153,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="26" customHeight="1">
+    <row r="104" ht="24" customHeight="1">
       <c r="A104" s="11" t="n">
         <v>98</v>
       </c>
@@ -6225,7 +6209,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="26" customHeight="1">
+    <row r="105" ht="24" customHeight="1">
       <c r="A105" s="7" t="n">
         <v>99</v>
       </c>
@@ -6281,7 +6265,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="26" customHeight="1">
+    <row r="106" ht="24" customHeight="1">
       <c r="A106" s="11" t="n">
         <v>100</v>
       </c>
@@ -6339,11 +6323,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B1:N1"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6360,23 +6344,23 @@
   <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
           <t>CALENDÁRIO DE RELATÓRIOS TRIMESTRAIS PASTORAIS — MCASD (2025 - 2026)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="35" customHeight="1">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Pastor</t>
@@ -6413,7 +6397,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Pr. Enoque Paulino</t>
@@ -6450,7 +6434,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Pr. Florindo Chiconjo</t>
@@ -6487,7 +6471,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Anc Simão Avelino</t>
@@ -6524,7 +6508,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Pr. Lauriano Salote</t>
@@ -6561,7 +6545,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Pr. Craveiro Idalino</t>
@@ -6598,7 +6582,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Pr. Aurélio de Jesus Jamba</t>
@@ -6635,7 +6619,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1">
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Pr. Emilio Cupua</t>
@@ -6672,7 +6656,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1">
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Pr. Vasco Aurélio Munga</t>
@@ -6709,7 +6693,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1">
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Pr. João Sangundu</t>
@@ -6746,7 +6730,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Pr. Evaristo P. Mendes</t>
@@ -6783,7 +6767,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Pr. José Silva Eurico</t>
@@ -6820,7 +6804,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Pr. Teles Justino de Oliveira</t>
@@ -6857,7 +6841,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Pr. Alfredo Casselo</t>
@@ -6894,7 +6878,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Pr. Tomás Tunguta</t>
@@ -6931,7 +6915,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
+    <row r="18" ht="22" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Pr. Agostinho Chalale</t>
@@ -6968,7 +6952,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
+    <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Pr. Fernando de Castro</t>
@@ -7005,7 +6989,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
+    <row r="20" ht="22" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Pr. Fernando Natal Pelé</t>
@@ -7042,7 +7026,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1">
+    <row r="21" ht="22" customHeight="1">
       <c r="A21" s="17" t="inlineStr">
         <is>
           <t>Pr. Miguel Evaldine Praia</t>
@@ -7079,7 +7063,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
+    <row r="22" ht="22" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Pr. Emílio Ernesto</t>
@@ -7116,7 +7100,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1">
+    <row r="23" ht="22" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Pr. Nelson M. Avelino</t>
@@ -7153,7 +7137,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1">
+    <row r="24" ht="22" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
           <t>Pr. Gomes João</t>
@@ -7190,7 +7174,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
+    <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
         <is>
           <t>Pr. Joaquim Chaves Cabral</t>
@@ -7227,7 +7211,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
+    <row r="26" ht="22" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Pr. Alberto C. Laurindo</t>
@@ -7264,7 +7248,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
+    <row r="27" ht="22" customHeight="1">
       <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Pr. Barnabé Daniel Fino</t>
@@ -7301,7 +7285,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
+    <row r="28" ht="22" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Pr. Adriano Delfim Feca</t>
@@ -7338,7 +7322,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1">
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Pr. Azevedo Manuel</t>
@@ -7375,7 +7359,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="24" customHeight="1">
+    <row r="30" ht="22" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
           <t>Pr. Frederico Valente</t>
@@ -7412,7 +7396,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1">
+    <row r="31" ht="22" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Pr. Henriques Mariano</t>
@@ -7449,7 +7433,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="24" customHeight="1">
+    <row r="32" ht="22" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
           <t>Pr. Distino Dinis Mulonde</t>
@@ -7486,7 +7470,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1">
+    <row r="33" ht="22" customHeight="1">
       <c r="A33" s="17" t="inlineStr">
         <is>
           <t>Pr. Emanuel Lucamba</t>
@@ -7523,7 +7507,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
+    <row r="34" ht="22" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
           <t>Pr. Erasmo Luvumba</t>
@@ -7560,7 +7544,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
+    <row r="35" ht="22" customHeight="1">
       <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Pr. Daniel Cameia</t>
@@ -7597,7 +7581,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1">
+    <row r="36" ht="22" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Pr. Martinho Sapato</t>
@@ -7634,7 +7618,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="24" customHeight="1">
+    <row r="37" ht="22" customHeight="1">
       <c r="A37" s="17" t="inlineStr">
         <is>
           <t>Pr. Ernesto M. Enoque</t>
@@ -7671,7 +7655,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="24" customHeight="1">
+    <row r="38" ht="22" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
           <t>Pr. Martins Menezes</t>
@@ -7708,7 +7692,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="24" customHeight="1">
+    <row r="39" ht="22" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
           <t>Pr. António Sebastião</t>
@@ -7745,7 +7729,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1">
+    <row r="40" ht="22" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
           <t>Pr. Roberto Cambinda</t>
@@ -7782,7 +7766,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="24" customHeight="1">
+    <row r="41" ht="22" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
           <t>Pr. Valentino Canguele</t>
@@ -7819,7 +7803,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="24" customHeight="1">
+    <row r="42" ht="22" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
           <t>Pr. Martinho Capela</t>
@@ -7856,7 +7840,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="24" customHeight="1">
+    <row r="43" ht="22" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
           <t>Pr. Domingos Suquina</t>
@@ -7893,7 +7877,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1">
+    <row r="44" ht="22" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
           <t>Pr. Francisco Lumbungululu</t>
@@ -7930,7 +7914,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="24" customHeight="1">
+    <row r="45" ht="22" customHeight="1">
       <c r="A45" s="17" t="inlineStr">
         <is>
           <t>Pr. Manuel Filipe Pacheco</t>
@@ -7967,7 +7951,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1">
+    <row r="46" ht="22" customHeight="1">
       <c r="A46" s="17" t="inlineStr">
         <is>
           <t>Pr. António Bambi</t>
@@ -8004,7 +7988,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="24" customHeight="1">
+    <row r="47" ht="22" customHeight="1">
       <c r="A47" s="17" t="inlineStr">
         <is>
           <t>Pr. Colino Celino</t>
@@ -8041,7 +8025,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="24" customHeight="1">
+    <row r="48" ht="22" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Pr. Samuel Catimba</t>
@@ -8078,7 +8062,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="24" customHeight="1">
+    <row r="49" ht="22" customHeight="1">
       <c r="A49" s="17" t="inlineStr">
         <is>
           <t>Pr. João Dinis José</t>
@@ -8115,7 +8099,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="24" customHeight="1">
+    <row r="50" ht="22" customHeight="1">
       <c r="A50" s="17" t="inlineStr">
         <is>
           <t>Pr. Nelito Manuel Jaime</t>
@@ -8152,7 +8136,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
+    <row r="51" ht="22" customHeight="1">
       <c r="A51" s="17" t="inlineStr">
         <is>
           <t>Pr. Justino Paulo</t>
@@ -8189,7 +8173,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="24" customHeight="1">
+    <row r="52" ht="22" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
         <is>
           <t>Pr. José Pereira Lemos</t>
@@ -8226,7 +8210,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="24" customHeight="1">
+    <row r="53" ht="22" customHeight="1">
       <c r="A53" s="17" t="inlineStr">
         <is>
           <t>Pr. Amadeu Cassoma</t>
@@ -8263,7 +8247,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="24" customHeight="1">
+    <row r="54" ht="22" customHeight="1">
       <c r="A54" s="17" t="inlineStr">
         <is>
           <t>Pr. Ambrósio Cangongo</t>
@@ -8300,7 +8284,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
+    <row r="55" ht="22" customHeight="1">
       <c r="A55" s="17" t="inlineStr">
         <is>
           <t>Pr. António Mário</t>
@@ -8337,7 +8321,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="24" customHeight="1">
+    <row r="56" ht="22" customHeight="1">
       <c r="A56" s="17" t="inlineStr">
         <is>
           <t>Pr. Baptista Mateus</t>
@@ -8374,7 +8358,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="24" customHeight="1">
+    <row r="57" ht="22" customHeight="1">
       <c r="A57" s="17" t="inlineStr">
         <is>
           <t>Pr. Gregório Henriques</t>
@@ -8411,7 +8395,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="24" customHeight="1">
+    <row r="58" ht="22" customHeight="1">
       <c r="A58" s="17" t="inlineStr">
         <is>
           <t>Pr. Madureira Chiwissi</t>
@@ -8448,7 +8432,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="24" customHeight="1">
+    <row r="59" ht="22" customHeight="1">
       <c r="A59" s="17" t="inlineStr">
         <is>
           <t>Pr. Pedro César</t>
@@ -8485,7 +8469,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="24" customHeight="1">
+    <row r="60" ht="22" customHeight="1">
       <c r="A60" s="17" t="inlineStr">
         <is>
           <t>Pr. Praia Ernesto</t>
@@ -8522,7 +8506,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="24" customHeight="1">
+    <row r="61" ht="22" customHeight="1">
       <c r="A61" s="17" t="inlineStr">
         <is>
           <t>Pr. Roberto Belarmino</t>
@@ -8559,7 +8543,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
+    <row r="62" ht="22" customHeight="1">
       <c r="A62" s="17" t="inlineStr">
         <is>
           <t>Pr. Sebastião João</t>
@@ -8596,7 +8580,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="24" customHeight="1">
+    <row r="63" ht="22" customHeight="1">
       <c r="A63" s="17" t="inlineStr">
         <is>
           <t>Pr. Tomás Morais Américo</t>
@@ -8633,7 +8617,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="24" customHeight="1">
+    <row r="64" ht="22" customHeight="1">
       <c r="A64" s="17" t="inlineStr">
         <is>
           <t>Pr. Francisco Fela</t>
@@ -8670,7 +8654,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="24" customHeight="1">
+    <row r="65" ht="22" customHeight="1">
       <c r="A65" s="17" t="inlineStr">
         <is>
           <t>Pr. Orlando Canema</t>
@@ -8707,7 +8691,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="24" customHeight="1">
+    <row r="66" ht="22" customHeight="1">
       <c r="A66" s="17" t="inlineStr">
         <is>
           <t>Pr. Vasco Arlindo Catengue</t>
@@ -8744,7 +8728,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="24" customHeight="1">
+    <row r="67" ht="22" customHeight="1">
       <c r="A67" s="17" t="inlineStr">
         <is>
           <t>Pr. Silva Moisés Joaquim</t>
@@ -8781,7 +8765,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="24" customHeight="1">
+    <row r="68" ht="22" customHeight="1">
       <c r="A68" s="17" t="inlineStr">
         <is>
           <t>Pr. Tiago de Jesus Faria</t>
@@ -8818,7 +8802,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="24" customHeight="1">
+    <row r="69" ht="22" customHeight="1">
       <c r="A69" s="17" t="inlineStr">
         <is>
           <t>Pr. Armando K. Gabriel</t>
@@ -8855,7 +8839,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="24" customHeight="1">
+    <row r="70" ht="22" customHeight="1">
       <c r="A70" s="17" t="inlineStr">
         <is>
           <t>Pr. Isaías Guilherme Mário</t>
@@ -8892,7 +8876,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="24" customHeight="1">
+    <row r="71" ht="22" customHeight="1">
       <c r="A71" s="17" t="inlineStr">
         <is>
           <t>Pr. Adelino Josué Celino</t>
@@ -8929,7 +8913,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="24" customHeight="1">
+    <row r="72" ht="22" customHeight="1">
       <c r="A72" s="17" t="inlineStr">
         <is>
           <t>Pr. Salomão Yondjunju</t>
@@ -8966,7 +8950,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="24" customHeight="1">
+    <row r="73" ht="22" customHeight="1">
       <c r="A73" s="17" t="inlineStr">
         <is>
           <t>Pr. João Sangando</t>
@@ -9003,7 +8987,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="24" customHeight="1">
+    <row r="74" ht="22" customHeight="1">
       <c r="A74" s="17" t="inlineStr">
         <is>
           <t>Pr. Alcides Rodrigues</t>
@@ -9040,7 +9024,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="24" customHeight="1">
+    <row r="75" ht="22" customHeight="1">
       <c r="A75" s="17" t="inlineStr">
         <is>
           <t>Pr. Malaquias Pedro</t>
@@ -9077,7 +9061,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="24" customHeight="1">
+    <row r="76" ht="22" customHeight="1">
       <c r="A76" s="17" t="inlineStr">
         <is>
           <t>Pr. Samuel Mahamba</t>
@@ -9114,7 +9098,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="24" customHeight="1">
+    <row r="77" ht="22" customHeight="1">
       <c r="A77" s="17" t="inlineStr">
         <is>
           <t>Pr. Agostinho Santos</t>
@@ -9151,7 +9135,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="24" customHeight="1">
+    <row r="78" ht="22" customHeight="1">
       <c r="A78" s="17" t="inlineStr">
         <is>
           <t>Pr. Avelino Ecumbi</t>
@@ -9188,7 +9172,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="24" customHeight="1">
+    <row r="79" ht="22" customHeight="1">
       <c r="A79" s="17" t="inlineStr">
         <is>
           <t>Pr. Paulino Cambuco</t>
@@ -9225,7 +9209,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="24" customHeight="1">
+    <row r="80" ht="22" customHeight="1">
       <c r="A80" s="17" t="inlineStr">
         <is>
           <t>Pr. Amílcar F. Gonçalves</t>
@@ -9262,7 +9246,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="24" customHeight="1">
+    <row r="81" ht="22" customHeight="1">
       <c r="A81" s="17" t="inlineStr">
         <is>
           <t>Pr. Armindo Graça Morais</t>
@@ -9299,7 +9283,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="24" customHeight="1">
+    <row r="82" ht="22" customHeight="1">
       <c r="A82" s="17" t="inlineStr">
         <is>
           <t>Pr. Bonifácio Chombe</t>
@@ -9336,7 +9320,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="24" customHeight="1">
+    <row r="83" ht="22" customHeight="1">
       <c r="A83" s="17" t="inlineStr">
         <is>
           <t>Pr. Orlando Sérgio José</t>
@@ -9373,7 +9357,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="24" customHeight="1">
+    <row r="84" ht="22" customHeight="1">
       <c r="A84" s="17" t="inlineStr">
         <is>
           <t>Pr. Galvão Vasco Chalale</t>
@@ -9410,7 +9394,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="24" customHeight="1">
+    <row r="85" ht="22" customHeight="1">
       <c r="A85" s="17" t="inlineStr">
         <is>
           <t>Anc. Feliciano Carlos</t>
@@ -9447,7 +9431,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="24" customHeight="1">
+    <row r="86" ht="22" customHeight="1">
       <c r="A86" s="17" t="inlineStr">
         <is>
           <t>Pr. Armando Tunguta</t>
@@ -9484,7 +9468,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="24" customHeight="1">
+    <row r="87" ht="22" customHeight="1">
       <c r="A87" s="17" t="inlineStr">
         <is>
           <t>Pr. Afonso Figura Cardoso</t>
@@ -9521,7 +9505,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="24" customHeight="1">
+    <row r="88" ht="22" customHeight="1">
       <c r="A88" s="17" t="inlineStr">
         <is>
           <t>Pr. Necas dos Santos</t>
@@ -9558,7 +9542,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="24" customHeight="1">
+    <row r="89" ht="22" customHeight="1">
       <c r="A89" s="17" t="inlineStr">
         <is>
           <t>Anc. Sabino Leo Sankulo</t>
@@ -9595,7 +9579,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="24" customHeight="1">
+    <row r="90" ht="22" customHeight="1">
       <c r="A90" s="17" t="inlineStr">
         <is>
           <t>Pr. Ermenegildo Sacanjala</t>
@@ -9632,7 +9616,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="24" customHeight="1">
+    <row r="91" ht="22" customHeight="1">
       <c r="A91" s="17" t="inlineStr">
         <is>
           <t>Pr. Jones Vitorino Dala</t>
@@ -9669,7 +9653,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="24" customHeight="1">
+    <row r="92" ht="22" customHeight="1">
       <c r="A92" s="17" t="inlineStr">
         <is>
           <t>Pr. Paulino Américo</t>
@@ -9706,7 +9690,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="24" customHeight="1">
+    <row r="93" ht="22" customHeight="1">
       <c r="A93" s="17" t="inlineStr">
         <is>
           <t>Pr. Alberto Vinhanga</t>
@@ -9743,7 +9727,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="24" customHeight="1">
+    <row r="94" ht="22" customHeight="1">
       <c r="A94" s="17" t="inlineStr">
         <is>
           <t>Pr. Mariano Ricardo Tomboco</t>
@@ -9780,7 +9764,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="24" customHeight="1">
+    <row r="95" ht="22" customHeight="1">
       <c r="A95" s="17" t="inlineStr">
         <is>
           <t>Pr. Francisco Cassucussuco</t>
@@ -9817,7 +9801,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="24" customHeight="1">
+    <row r="96" ht="22" customHeight="1">
       <c r="A96" s="17" t="inlineStr">
         <is>
           <t>Pr. Severiano Chicolomhuenho</t>
@@ -9854,7 +9838,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="24" customHeight="1">
+    <row r="97" ht="22" customHeight="1">
       <c r="A97" s="17" t="inlineStr">
         <is>
           <t>Pr. Lauriano Quelino</t>
@@ -9891,7 +9875,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="24" customHeight="1">
+    <row r="98" ht="22" customHeight="1">
       <c r="A98" s="17" t="inlineStr">
         <is>
           <t>Pr. Daniel Chionga Cameia</t>
@@ -9928,7 +9912,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="24" customHeight="1">
+    <row r="99" ht="22" customHeight="1">
       <c r="A99" s="17" t="inlineStr">
         <is>
           <t>Pr. Diamantino Sawambo</t>
@@ -9965,7 +9949,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="24" customHeight="1">
+    <row r="100" ht="22" customHeight="1">
       <c r="A100" s="17" t="inlineStr">
         <is>
           <t>Pr. Tchindongo Djimbo</t>
@@ -10002,7 +9986,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="24" customHeight="1">
+    <row r="101" ht="22" customHeight="1">
       <c r="A101" s="17" t="inlineStr">
         <is>
           <t>Pr. Isaias Sabonete</t>
@@ -10039,7 +10023,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="24" customHeight="1">
+    <row r="102" ht="22" customHeight="1">
       <c r="A102" s="17" t="inlineStr">
         <is>
           <t>Pr. Nicolau Jacob Soma</t>
@@ -10076,7 +10060,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="24" customHeight="1">
+    <row r="103" ht="22" customHeight="1">
       <c r="A103" s="17" t="inlineStr">
         <is>
           <t>Pr. Eugénio Capiñgala Manuel</t>
@@ -10115,7 +10099,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -10125,343 +10108,151 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>MISSÃO DAS IGREJAS ADVENTISTAS DO SÉTIMO DIA DA UNIÃO SUDOESTE DE ANGOLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>PAINEL EXECUTIVO DE AVALIAÇÃO PASTORAL E MAPEAMENTO DISTRITAL 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>✨ SISTEMA PREMIUM CONCEBIDO E DESENVOLVIDO POR: VALENTINO CANGUELE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TOTAL DE PASTORES</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CONGREGAÇÕES MAPEADAS</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MÉDIA GERAL DA MISSÃO</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>CLASSIFICAÇÃO PREDOMINANTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>PAINEL EXECUTIVO &amp; RESUMO ESTRATÉGICO — MCASD 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Indicador Chave (KPI)</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Valor Atual</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Meta 2026</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>Estado institucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Total de Pastores no Quadro</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>100 Pastores</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>100 Pastores</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>100% Alcançado</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Total de Congregações Mapeadas</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>330 Congregações</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>350 Congregações</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>94% Alcançado</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Média Geral de Desempenho</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>4.52 / 5.00</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>4.50 / 5.00</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>Acima da Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Classificação Geral da Missão</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>MUITO BOM (MB)</t>
         </is>
       </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>🔍 CONSULTA RÁPIDA DE PASTOR (FILTRO INDIVIDUAL PREMIUM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SELECIONAR PASTOR:</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Pr. Enoque Paulino</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>PONTUAÇÃO TOTAL:</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DISTRITO / FUNÇÃO:</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>MÉDIA GERAL FINAL:</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PROVÍNCIA / CARGO:</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CLASSIFICAÇÃO:</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CONTACTO TELEFÓNICO:</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STATUS FICHA:</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DESEMPENHO GLOBAL POR ÁREA DE AVALIAÇÃO PASTORAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Área de Avaliação</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nº de Critérios</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Pontuação Máx</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Média da Missão</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>% de Aproveitamento</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Classificação Geral</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1. Assistência Pastoral</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>11</v>
-      </c>
-      <c r="D16" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2. Relacionamento Pessoal</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>11</v>
-      </c>
-      <c r="D17" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3. Família Pastoral</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>4. Sermões</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>5. Administração</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>16</v>
-      </c>
-      <c r="D20" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>RESUMO DA COBERTURA PASTORAL POR PROVÍNCIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Província</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Pastores Alocados</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>% do Quadro</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Média de Desempenho</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Província do Huambo</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Ativo &amp; Mapeado</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Província do Bié</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Ativo &amp; Mapeado</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Província do Cubango</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Ativo &amp; Mapeado</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Província do Quando</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Ativo &amp; Mapeado</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Outras Regiões / Missões</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Ativo &amp; Mapeado</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TOTAL GERAL</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>100% Concluído</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>MCASD 2026 PREMIUM EDITION | SISTEMATIZADO E DESENVOLVIDO POR VALENTINO CANGUELE</t>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>EXCELENTE (E)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>Em Evolução</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Relatórios Trimestrais Sincronizados</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Sincronizado Supabase Cloud</t>
         </is>
       </c>
     </row>
@@ -10476,1676 +10267,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>FICHA DE AVALIAÇÃO PASTORAL - MCASD 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SELEÇÃO DO PASTOR:</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Pr. Enoque Paulino</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>RESUMO DA AVALIAÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DISTRITO / FUNÇÃO:</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Pontuação Total:</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PROVÍNCIA:</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Pontuação Máxima:</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>255 PONTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LICENÇA / CARGO:</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Média Geral Final:</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CONTACTO:</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CLASSIFICAÇÃO:</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>"O pensamento de que precisamos melhorar cada dia nos inspira a buscar o melhor de nós mesmos. Tal crescimento não é possível sem uma visão clara de nossos pontos fortes e dos que precisam ser melhorados. O instrumento mais eficiente para este diagnóstico, sem dúvida, é a avaliação contínua. Por isso queremos contar com a colaboração do (a) irmão (ã) no sentido de dar o seu parecer avaliativo sobre o trabalho pastoral. Obrigado por colaborar para que o ministério do seu pastor seja mais eficiente."</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ESCALA DE AVALIAÇÃO: 1 = Deficiente (D)  |  2 = Regular (R)  |  3 = Bom (B)  |  4 = Muito Bom (MB)  |  5 = Excelente (E)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1. ASSISTÊNCIA PASTORAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Nº  |  CRITÉRIO DE AVALIAÇÃO</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>D (1)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>R (2)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>B (3)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>MB (4)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>E (5)</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>NOTA ATRIBUÍDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1.  Pontualidade nos Cultos e Reuniões</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2.  Visitação</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3.  Aconselhamento</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>4.  Espiritualidade refletida</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>5.  Freqüência às atividades espirituais da igreja</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" t="n">
-        <v>4</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5</v>
-      </c>
-      <c r="H18" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6.  Freqüência às atividades sociais da igreja</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" t="n">
-        <v>4</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>7.  Apoio às atividades dos Jovens</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G20" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>8.  Habilidade em resolver conflitos</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>9.  Estudioso e com vontade de Aprender</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>10.  Preparo Intelectual</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>11.  Demonstra Vocação Pastoral</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" t="n">
-        <v>4</v>
-      </c>
-      <c r="G24" t="n">
-        <v>5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>MÉDIA DA ÁREA (1. Assistência Pastoral):</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2. RELACIONAMENTO PESSOAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Nº  |  CRITÉRIO DE AVALIAÇÃO</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>D (1)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>R (2)</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>B (3)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>MB (4)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>E (5)</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>NOTA ATRIBUÍDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1.  Cuidado na Higiene Pessoal</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" t="n">
-        <v>4</v>
-      </c>
-      <c r="G29" t="n">
-        <v>5</v>
-      </c>
-      <c r="H29" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2.  Vestir-se Adequadamente</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>3</v>
-      </c>
-      <c r="F30" t="n">
-        <v>4</v>
-      </c>
-      <c r="G30" t="n">
-        <v>5</v>
-      </c>
-      <c r="H30" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>3.  Representa bem a igreja na comunidade</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" t="n">
-        <v>4</v>
-      </c>
-      <c r="G31" t="n">
-        <v>5</v>
-      </c>
-      <c r="H31" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>4.  Atenção e Cortesia no trato com os membros</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" t="n">
-        <v>3</v>
-      </c>
-      <c r="F32" t="n">
-        <v>4</v>
-      </c>
-      <c r="G32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H32" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>5.  Entusiasmo e bom humor</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" t="n">
-        <v>4</v>
-      </c>
-      <c r="G33" t="n">
-        <v>5</v>
-      </c>
-      <c r="H33" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>6.  Confiabilidade</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" t="n">
-        <v>3</v>
-      </c>
-      <c r="F34" t="n">
-        <v>4</v>
-      </c>
-      <c r="G34" t="n">
-        <v>5</v>
-      </c>
-      <c r="H34" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>7.  Demonstração de Amizade</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" t="n">
-        <v>3</v>
-      </c>
-      <c r="F35" t="n">
-        <v>4</v>
-      </c>
-      <c r="G35" t="n">
-        <v>5</v>
-      </c>
-      <c r="H35" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>8.  Humildade</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" t="n">
-        <v>3</v>
-      </c>
-      <c r="F36" t="n">
-        <v>4</v>
-      </c>
-      <c r="G36" t="n">
-        <v>5</v>
-      </c>
-      <c r="H36" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>9.  Cortesia</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>3</v>
-      </c>
-      <c r="F37" t="n">
-        <v>4</v>
-      </c>
-      <c r="G37" t="n">
-        <v>5</v>
-      </c>
-      <c r="H37" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>10.  Otimismo</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" t="n">
-        <v>3</v>
-      </c>
-      <c r="F38" t="n">
-        <v>4</v>
-      </c>
-      <c r="G38" t="n">
-        <v>5</v>
-      </c>
-      <c r="H38" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>11.  Maturidade e Responsabilidade</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" t="n">
-        <v>4</v>
-      </c>
-      <c r="G39" t="n">
-        <v>5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>MÉDIA DA ÁREA (2. Relacionamento Pessoal):</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>3. FAMÍLIA PASTORAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Nº  |  CRITÉRIO DE AVALIAÇÃO</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>D (1)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>R (2)</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>B (3)</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>MB (4)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>E (5)</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>NOTA ATRIBUÍDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>1.  Relacionamento com a família</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E44" t="n">
-        <v>3</v>
-      </c>
-      <c r="F44" t="n">
-        <v>4</v>
-      </c>
-      <c r="G44" t="n">
-        <v>5</v>
-      </c>
-      <c r="H44" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2.  Envolvimento da Esposa nas Atividades da Igreja</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" t="n">
-        <v>4</v>
-      </c>
-      <c r="G45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H45" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>3.  Testemunho da esposa com os princípios da Igreja</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E46" t="n">
-        <v>3</v>
-      </c>
-      <c r="F46" t="n">
-        <v>4</v>
-      </c>
-      <c r="G46" t="n">
-        <v>5</v>
-      </c>
-      <c r="H46" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>4.  Testemunho dos Filhos</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E47" t="n">
-        <v>3</v>
-      </c>
-      <c r="F47" t="n">
-        <v>4</v>
-      </c>
-      <c r="G47" t="n">
-        <v>5</v>
-      </c>
-      <c r="H47" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>5.  Administra bem as Finanças da Família</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E48" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" t="n">
-        <v>4</v>
-      </c>
-      <c r="G48" t="n">
-        <v>5</v>
-      </c>
-      <c r="H48" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MÉDIA DA ÁREA (3. Família Pastoral):</t>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>COMENTÁRIOS E OBSERVAÇÕES SOBRE A FAMÍLIA PASTORAL:</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>____________________________________________________________________________________________________</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>____________________________________________________________________________________________________</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>____________________________________________________________________________________________________</t>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>4. SERMÕES</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Nº  |  CRITÉRIO DE AVALIAÇÃO</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>D (1)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>R (2)</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>B (3)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>MB (4)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>E (5)</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>NOTA ATRIBUÍDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>1.  Claros e Convincentes</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2</v>
-      </c>
-      <c r="E58" t="n">
-        <v>3</v>
-      </c>
-      <c r="F58" t="n">
-        <v>4</v>
-      </c>
-      <c r="G58" t="n">
-        <v>5</v>
-      </c>
-      <c r="H58" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2.  Cristocêntricos</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="n">
-        <v>2</v>
-      </c>
-      <c r="E59" t="n">
-        <v>3</v>
-      </c>
-      <c r="F59" t="n">
-        <v>4</v>
-      </c>
-      <c r="G59" t="n">
-        <v>5</v>
-      </c>
-      <c r="H59" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>3.  Conteúdo adequado às necessidades dos membros</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="n">
-        <v>2</v>
-      </c>
-      <c r="E60" t="n">
-        <v>3</v>
-      </c>
-      <c r="F60" t="n">
-        <v>4</v>
-      </c>
-      <c r="G60" t="n">
-        <v>5</v>
-      </c>
-      <c r="H60" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>4.  Bem organizados</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" t="n">
-        <v>3</v>
-      </c>
-      <c r="F61" t="n">
-        <v>4</v>
-      </c>
-      <c r="G61" t="n">
-        <v>5</v>
-      </c>
-      <c r="H61" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>5.  Dentro do tempo</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="n">
-        <v>2</v>
-      </c>
-      <c r="E62" t="n">
-        <v>3</v>
-      </c>
-      <c r="F62" t="n">
-        <v>4</v>
-      </c>
-      <c r="G62" t="n">
-        <v>5</v>
-      </c>
-      <c r="H62" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>6.  Espontâneo ao pregar</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2</v>
-      </c>
-      <c r="E63" t="n">
-        <v>3</v>
-      </c>
-      <c r="F63" t="n">
-        <v>4</v>
-      </c>
-      <c r="G63" t="n">
-        <v>5</v>
-      </c>
-      <c r="H63" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>7.  Pregador Equilibrado</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="n">
-        <v>2</v>
-      </c>
-      <c r="E64" t="n">
-        <v>3</v>
-      </c>
-      <c r="F64" t="n">
-        <v>4</v>
-      </c>
-      <c r="G64" t="n">
-        <v>5</v>
-      </c>
-      <c r="H64" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>8.  Tem Plano (calendário) de pregação</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="n">
-        <v>2</v>
-      </c>
-      <c r="E65" t="n">
-        <v>3</v>
-      </c>
-      <c r="F65" t="n">
-        <v>4</v>
-      </c>
-      <c r="G65" t="n">
-        <v>5</v>
-      </c>
-      <c r="H65" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>MÉDIA DA ÁREA (4. Sermões):</t>
-        </is>
-      </c>
-    </row>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>5. ADMINISTRAÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Nº  |  CRITÉRIO DE AVALIAÇÃO</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>D (1)</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>R (2)</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>B (3)</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>MB (4)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>E (5)</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>NOTA ATRIBUÍDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>1.  Pontualidade</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="n">
-        <v>2</v>
-      </c>
-      <c r="E70" t="n">
-        <v>3</v>
-      </c>
-      <c r="F70" t="n">
-        <v>4</v>
-      </c>
-      <c r="G70" t="n">
-        <v>5</v>
-      </c>
-      <c r="H70" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2.  Organização</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" t="n">
-        <v>2</v>
-      </c>
-      <c r="E71" t="n">
-        <v>3</v>
-      </c>
-      <c r="F71" t="n">
-        <v>4</v>
-      </c>
-      <c r="G71" t="n">
-        <v>5</v>
-      </c>
-      <c r="H71" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>3.  Imparcialidade</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" t="n">
-        <v>2</v>
-      </c>
-      <c r="E72" t="n">
-        <v>3</v>
-      </c>
-      <c r="F72" t="n">
-        <v>4</v>
-      </c>
-      <c r="G72" t="n">
-        <v>5</v>
-      </c>
-      <c r="H72" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>4.  Iniciativa</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" t="n">
-        <v>2</v>
-      </c>
-      <c r="E73" t="n">
-        <v>3</v>
-      </c>
-      <c r="F73" t="n">
-        <v>4</v>
-      </c>
-      <c r="G73" t="n">
-        <v>5</v>
-      </c>
-      <c r="H73" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>5.  Delegação de Responsabilidades</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" t="n">
-        <v>2</v>
-      </c>
-      <c r="E74" t="n">
-        <v>3</v>
-      </c>
-      <c r="F74" t="n">
-        <v>4</v>
-      </c>
-      <c r="G74" t="n">
-        <v>5</v>
-      </c>
-      <c r="H74" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>6.  Dirigi bem a Comissão da Igreja</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" t="n">
-        <v>2</v>
-      </c>
-      <c r="E75" t="n">
-        <v>3</v>
-      </c>
-      <c r="F75" t="n">
-        <v>4</v>
-      </c>
-      <c r="G75" t="n">
-        <v>5</v>
-      </c>
-      <c r="H75" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>7.  Atualizado com as finanças da igreja</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" t="n">
-        <v>2</v>
-      </c>
-      <c r="E76" t="n">
-        <v>3</v>
-      </c>
-      <c r="F76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G76" t="n">
-        <v>5</v>
-      </c>
-      <c r="H76" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>8.  Acompanhamento das atividades da igreja</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" t="n">
-        <v>2</v>
-      </c>
-      <c r="E77" t="n">
-        <v>3</v>
-      </c>
-      <c r="F77" t="n">
-        <v>4</v>
-      </c>
-      <c r="G77" t="n">
-        <v>5</v>
-      </c>
-      <c r="H77" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>9.  Promoção das Atividades da Igreja</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="n">
-        <v>2</v>
-      </c>
-      <c r="E78" t="n">
-        <v>3</v>
-      </c>
-      <c r="F78" t="n">
-        <v>4</v>
-      </c>
-      <c r="G78" t="n">
-        <v>5</v>
-      </c>
-      <c r="H78" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>10.  Comunicação com a Liderança</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="n">
-        <v>2</v>
-      </c>
-      <c r="E79" t="n">
-        <v>3</v>
-      </c>
-      <c r="F79" t="n">
-        <v>4</v>
-      </c>
-      <c r="G79" t="n">
-        <v>5</v>
-      </c>
-      <c r="H79" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>11.  Liderança e motivação do grupo</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="n">
-        <v>2</v>
-      </c>
-      <c r="E80" t="n">
-        <v>3</v>
-      </c>
-      <c r="F80" t="n">
-        <v>4</v>
-      </c>
-      <c r="G80" t="n">
-        <v>5</v>
-      </c>
-      <c r="H80" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>12.  Treinamento e orientação</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="n">
-        <v>2</v>
-      </c>
-      <c r="E81" t="n">
-        <v>3</v>
-      </c>
-      <c r="F81" t="n">
-        <v>4</v>
-      </c>
-      <c r="G81" t="n">
-        <v>5</v>
-      </c>
-      <c r="H81" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>13.  Fidelidade aos regulamentos da Igreja</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="n">
-        <v>2</v>
-      </c>
-      <c r="E82" t="n">
-        <v>3</v>
-      </c>
-      <c r="F82" t="n">
-        <v>4</v>
-      </c>
-      <c r="G82" t="n">
-        <v>5</v>
-      </c>
-      <c r="H82" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>14.  Planejamento Anual para o distrito</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" t="n">
-        <v>2</v>
-      </c>
-      <c r="E83" t="n">
-        <v>3</v>
-      </c>
-      <c r="F83" t="n">
-        <v>4</v>
-      </c>
-      <c r="G83" t="n">
-        <v>5</v>
-      </c>
-      <c r="H83" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>15.  Planejamento das atividades evangelísticas</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" t="n">
-        <v>2</v>
-      </c>
-      <c r="E84" t="n">
-        <v>3</v>
-      </c>
-      <c r="F84" t="n">
-        <v>4</v>
-      </c>
-      <c r="G84" t="n">
-        <v>5</v>
-      </c>
-      <c r="H84" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>16.  Trabalho junto com a liderança</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="n">
-        <v>2</v>
-      </c>
-      <c r="E85" t="n">
-        <v>3</v>
-      </c>
-      <c r="F85" t="n">
-        <v>4</v>
-      </c>
-      <c r="G85" t="n">
-        <v>5</v>
-      </c>
-      <c r="H85" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>MÉDIA DA ÁREA (5. Administração):</t>
-        </is>
-      </c>
-    </row>
-    <row r="87"/>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data da Avaliação: ____ / ____ / 2026</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Sistema Concebido por: Valentino Canguele</t>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>FICHA DE AVALIAÇÃO PASTORAL — MODELO INSTITUCIONAL (51 CRITÉRIOS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Nº Item</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Critério de Avaliação</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Categoria / Área</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>Descrição do Critério</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>Escala de Pontuação</t>
         </is>
       </c>
     </row>
@@ -12163,49 +10325,52 @@
   <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>IGREJA ADVENTISTA DO 7º DIA</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="15" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>UNIÃO SUDOESTE DE ANGOLA</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>MISSÃO CENTRO</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>RELATÓRIO TRIMESTRAL DA ASSOCIAÇÃO PASTORAL</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="22" customHeight="1"/>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>PASTOR DO DISTRITO:</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Pr. Enoque Paulino</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
+    <row r="7" ht="22" customHeight="1"/>
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>Nº</t>
@@ -12222,7 +10387,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" t="n">
         <v>1</v>
       </c>
@@ -12235,7 +10400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" t="n">
         <v>2</v>
       </c>
@@ -12248,7 +10413,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" t="n">
         <v>3</v>
       </c>
@@ -12261,7 +10426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" t="n">
         <v>4</v>
       </c>
@@ -12274,7 +10439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -12286,7 +10451,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" t="n">
         <v>5</v>
       </c>
@@ -12299,14 +10464,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
           <t>II.  MISSÃO GLOBAL EVANGELISTA</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" t="n">
         <v>6</v>
       </c>
@@ -12319,7 +10484,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" t="n">
         <v>7</v>
       </c>
@@ -12332,7 +10497,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="22" customHeight="1">
       <c r="A18" t="n">
         <v>8</v>
       </c>
@@ -12345,7 +10510,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="22" customHeight="1">
       <c r="A19" t="n">
         <v>9</v>
       </c>
@@ -12358,7 +10523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="22" customHeight="1">
       <c r="A20" t="n">
         <v>10</v>
       </c>
@@ -12371,7 +10536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="22" customHeight="1">
       <c r="A21" t="n">
         <v>11</v>
       </c>
@@ -12384,7 +10549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="22" customHeight="1">
       <c r="A22" t="n">
         <v>12</v>
       </c>
@@ -12397,7 +10562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="22" customHeight="1">
       <c r="A23" t="n">
         <v>13</v>
       </c>
@@ -12410,7 +10575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="22" customHeight="1">
       <c r="A24" t="n">
         <v>14</v>
       </c>
@@ -12423,7 +10588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="22" customHeight="1">
       <c r="A25" t="n">
         <v>15</v>
       </c>
@@ -12438,7 +10603,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="22" customHeight="1">
       <c r="A26" t="n">
         <v>16</v>
       </c>
@@ -12451,7 +10616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="22" customHeight="1">
       <c r="A27" t="n">
         <v>17</v>
       </c>
@@ -12464,7 +10629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="22" customHeight="1">
       <c r="A28" t="n">
         <v>18</v>
       </c>
@@ -12477,7 +10642,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" t="n">
         <v>19</v>
       </c>
@@ -12490,7 +10655,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="22" customHeight="1">
       <c r="A30" t="n">
         <v>20</v>
       </c>
@@ -12503,7 +10668,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="22" customHeight="1">
       <c r="A31" t="n">
         <v>21</v>
       </c>
@@ -12516,7 +10681,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="22" customHeight="1">
       <c r="A32" t="n">
         <v>22</v>
       </c>
@@ -12529,7 +10694,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="22" customHeight="1">
       <c r="A33" t="n">
         <v>23</v>
       </c>
@@ -12542,7 +10707,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="22" customHeight="1">
       <c r="A34" t="n">
         <v>24</v>
       </c>
@@ -12555,7 +10720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="22" customHeight="1">
       <c r="A35" t="n">
         <v>25</v>
       </c>
@@ -12568,7 +10733,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="22" customHeight="1">
       <c r="A36" t="n">
         <v>26</v>
       </c>
@@ -12581,7 +10746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="22" customHeight="1">
       <c r="A37" t="n">
         <v>27</v>
       </c>
@@ -12594,7 +10759,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="22" customHeight="1">
       <c r="A38" t="n">
         <v>28</v>
       </c>
@@ -12607,29 +10772,29 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
+    <row r="39" ht="22" customHeight="1"/>
+    <row r="40" ht="22" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
           <t>_______________________, _______, __________________________, 2026</t>
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="22" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
           <t>Assinatura do Pastor</t>
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="22" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
           <t>_______________________________________</t>
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="22" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
           <t>Ficha de Relatório Impresso | Sistematizado por Valentino Canguele</t>
@@ -12650,143 +10815,148 @@
   <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>LISTA TELEFÓNICA E CADASTRO DOS PASTORES DA MCASD - 2026</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="15" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>Desenvolvido por Valentino Canguele - Missão das Igrejas Adventistas do Sétimo Dia</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Nº</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Nome do Pastor</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Distrito / Função</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>Província</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>Licença / Cargo</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>Contacto Telefónico</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Pr. Enoque Paulino</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Presidente - Missão</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Huambo</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Huambo</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Presidente</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>924242887</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Pr. Florindo Chiconjo</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Secretário</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Huambo</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Huambo</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>Secretário Executivo</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>924074666</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Anc Simão Avelino</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Tesoureiro</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Huambo</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Huambo</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>Tesoureiro</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>929744811</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" t="n">
         <v>4</v>
       </c>
@@ -12816,7 +10986,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" t="n">
         <v>5</v>
       </c>
@@ -12846,7 +11016,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" t="n">
         <v>6</v>
       </c>
@@ -12876,7 +11046,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" t="n">
         <v>7</v>
       </c>
@@ -12906,7 +11076,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" t="n">
         <v>8</v>
       </c>
@@ -12936,7 +11106,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" t="n">
         <v>9</v>
       </c>
@@ -12966,7 +11136,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" t="n">
         <v>10</v>
       </c>
@@ -12996,7 +11166,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" t="n">
         <v>11</v>
       </c>
@@ -13026,7 +11196,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" t="n">
         <v>12</v>
       </c>
@@ -13056,7 +11226,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" t="n">
         <v>13</v>
       </c>
@@ -13086,7 +11256,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" t="n">
         <v>14</v>
       </c>
@@ -13116,7 +11286,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="22" customHeight="1">
       <c r="A18" t="n">
         <v>15</v>
       </c>
@@ -13146,7 +11316,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="22" customHeight="1">
       <c r="A19" t="n">
         <v>16</v>
       </c>
@@ -13176,7 +11346,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="22" customHeight="1">
       <c r="A20" t="n">
         <v>17</v>
       </c>
@@ -13206,7 +11376,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="22" customHeight="1">
       <c r="A21" t="n">
         <v>18</v>
       </c>
@@ -13236,7 +11406,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="22" customHeight="1">
       <c r="A22" t="n">
         <v>19</v>
       </c>
@@ -13266,7 +11436,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="22" customHeight="1">
       <c r="A23" t="n">
         <v>20</v>
       </c>
@@ -13296,7 +11466,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="22" customHeight="1">
       <c r="A24" t="n">
         <v>21</v>
       </c>
@@ -13326,7 +11496,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="22" customHeight="1">
       <c r="A25" t="n">
         <v>22</v>
       </c>
@@ -13356,7 +11526,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="22" customHeight="1">
       <c r="A26" t="n">
         <v>23</v>
       </c>
@@ -13386,7 +11556,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="22" customHeight="1">
       <c r="A27" t="n">
         <v>24</v>
       </c>
@@ -13416,7 +11586,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="22" customHeight="1">
       <c r="A28" t="n">
         <v>25</v>
       </c>
@@ -13446,7 +11616,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" t="n">
         <v>26</v>
       </c>
@@ -13476,7 +11646,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="22" customHeight="1">
       <c r="A30" t="n">
         <v>27</v>
       </c>
@@ -13506,7 +11676,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="22" customHeight="1">
       <c r="A31" t="n">
         <v>28</v>
       </c>
@@ -13536,7 +11706,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="22" customHeight="1">
       <c r="A32" t="n">
         <v>29</v>
       </c>
@@ -13566,7 +11736,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="22" customHeight="1">
       <c r="A33" t="n">
         <v>30</v>
       </c>
@@ -13596,7 +11766,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="22" customHeight="1">
       <c r="A34" t="n">
         <v>31</v>
       </c>
@@ -13626,7 +11796,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="22" customHeight="1">
       <c r="A35" t="n">
         <v>32</v>
       </c>
@@ -13656,7 +11826,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="22" customHeight="1">
       <c r="A36" t="n">
         <v>33</v>
       </c>
@@ -13686,7 +11856,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="22" customHeight="1">
       <c r="A37" t="n">
         <v>34</v>
       </c>
@@ -13716,7 +11886,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="22" customHeight="1">
       <c r="A38" t="n">
         <v>35</v>
       </c>
@@ -13746,7 +11916,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="22" customHeight="1">
       <c r="A39" t="n">
         <v>36</v>
       </c>
@@ -13776,7 +11946,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="22" customHeight="1">
       <c r="A40" t="n">
         <v>37</v>
       </c>
@@ -13806,7 +11976,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="22" customHeight="1">
       <c r="A41" t="n">
         <v>38</v>
       </c>
@@ -13836,7 +12006,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="22" customHeight="1">
       <c r="A42" t="n">
         <v>39</v>
       </c>
@@ -13866,7 +12036,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="22" customHeight="1">
       <c r="A43" t="n">
         <v>40</v>
       </c>
@@ -13896,7 +12066,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="22" customHeight="1">
       <c r="A44" t="n">
         <v>41</v>
       </c>
@@ -13926,7 +12096,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="22" customHeight="1">
       <c r="A45" t="n">
         <v>42</v>
       </c>
@@ -13956,7 +12126,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="22" customHeight="1">
       <c r="A46" t="n">
         <v>43</v>
       </c>
@@ -13986,7 +12156,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="22" customHeight="1">
       <c r="A47" t="n">
         <v>44</v>
       </c>
@@ -14016,7 +12186,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="22" customHeight="1">
       <c r="A48" t="n">
         <v>45</v>
       </c>
@@ -14046,7 +12216,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="22" customHeight="1">
       <c r="A49" t="n">
         <v>46</v>
       </c>
@@ -14076,7 +12246,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="22" customHeight="1">
       <c r="A50" t="n">
         <v>47</v>
       </c>
@@ -14106,7 +12276,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="22" customHeight="1">
       <c r="A51" t="n">
         <v>48</v>
       </c>
@@ -14136,7 +12306,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="22" customHeight="1">
       <c r="A52" t="n">
         <v>49</v>
       </c>
@@ -14166,7 +12336,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="22" customHeight="1">
       <c r="A53" t="n">
         <v>50</v>
       </c>
@@ -14196,7 +12366,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="22" customHeight="1">
       <c r="A54" t="n">
         <v>51</v>
       </c>
@@ -14226,7 +12396,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="22" customHeight="1">
       <c r="A55" t="n">
         <v>52</v>
       </c>
@@ -14256,7 +12426,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="22" customHeight="1">
       <c r="A56" t="n">
         <v>53</v>
       </c>
@@ -14286,7 +12456,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="22" customHeight="1">
       <c r="A57" t="n">
         <v>54</v>
       </c>
@@ -14316,7 +12486,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="22" customHeight="1">
       <c r="A58" t="n">
         <v>55</v>
       </c>
@@ -14346,7 +12516,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="22" customHeight="1">
       <c r="A59" t="n">
         <v>56</v>
       </c>
@@ -14376,7 +12546,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="22" customHeight="1">
       <c r="A60" t="n">
         <v>57</v>
       </c>
@@ -14406,7 +12576,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="22" customHeight="1">
       <c r="A61" t="n">
         <v>58</v>
       </c>
@@ -14436,7 +12606,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="22" customHeight="1">
       <c r="A62" t="n">
         <v>59</v>
       </c>
@@ -14466,7 +12636,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="22" customHeight="1">
       <c r="A63" t="n">
         <v>60</v>
       </c>
@@ -14496,7 +12666,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="22" customHeight="1">
       <c r="A64" t="n">
         <v>61</v>
       </c>
@@ -14526,7 +12696,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="22" customHeight="1">
       <c r="A65" t="n">
         <v>62</v>
       </c>
@@ -14556,7 +12726,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="22" customHeight="1">
       <c r="A66" t="n">
         <v>63</v>
       </c>
@@ -14586,7 +12756,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="22" customHeight="1">
       <c r="A67" t="n">
         <v>64</v>
       </c>
@@ -14616,7 +12786,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="22" customHeight="1">
       <c r="A68" t="n">
         <v>65</v>
       </c>
@@ -14646,7 +12816,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="22" customHeight="1">
       <c r="A69" t="n">
         <v>66</v>
       </c>
@@ -14676,7 +12846,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="22" customHeight="1">
       <c r="A70" t="n">
         <v>67</v>
       </c>
@@ -14706,7 +12876,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="22" customHeight="1">
       <c r="A71" t="n">
         <v>68</v>
       </c>
@@ -14736,7 +12906,7 @@
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="22" customHeight="1">
       <c r="A72" t="n">
         <v>69</v>
       </c>
@@ -14766,7 +12936,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="22" customHeight="1">
       <c r="A73" t="n">
         <v>70</v>
       </c>
@@ -14796,7 +12966,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="22" customHeight="1">
       <c r="A74" t="n">
         <v>71</v>
       </c>
@@ -14826,7 +12996,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="22" customHeight="1">
       <c r="A75" t="n">
         <v>72</v>
       </c>
@@ -14856,7 +13026,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="22" customHeight="1">
       <c r="A76" t="n">
         <v>73</v>
       </c>
@@ -14886,7 +13056,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="22" customHeight="1">
       <c r="A77" t="n">
         <v>74</v>
       </c>
@@ -14916,7 +13086,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="22" customHeight="1">
       <c r="A78" t="n">
         <v>75</v>
       </c>
@@ -14946,7 +13116,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="22" customHeight="1">
       <c r="A79" t="n">
         <v>76</v>
       </c>
@@ -14976,7 +13146,7 @@
         </is>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="22" customHeight="1">
       <c r="A80" t="n">
         <v>77</v>
       </c>
@@ -15006,7 +13176,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="22" customHeight="1">
       <c r="A81" t="n">
         <v>78</v>
       </c>
@@ -15036,7 +13206,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="22" customHeight="1">
       <c r="A82" t="n">
         <v>79</v>
       </c>
@@ -15066,7 +13236,7 @@
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="22" customHeight="1">
       <c r="A83" t="n">
         <v>80</v>
       </c>
@@ -15096,7 +13266,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="22" customHeight="1">
       <c r="A84" t="n">
         <v>81</v>
       </c>
@@ -15126,7 +13296,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="22" customHeight="1">
       <c r="A85" t="n">
         <v>82</v>
       </c>
@@ -15156,7 +13326,7 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="22" customHeight="1">
       <c r="A86" t="n">
         <v>83</v>
       </c>
@@ -15186,7 +13356,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="22" customHeight="1">
       <c r="A87" t="n">
         <v>84</v>
       </c>
@@ -15216,7 +13386,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="22" customHeight="1">
       <c r="A88" t="n">
         <v>85</v>
       </c>
@@ -15246,7 +13416,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="22" customHeight="1">
       <c r="A89" t="n">
         <v>86</v>
       </c>
@@ -15276,7 +13446,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="22" customHeight="1">
       <c r="A90" t="n">
         <v>87</v>
       </c>
@@ -15306,7 +13476,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="22" customHeight="1">
       <c r="A91" t="n">
         <v>88</v>
       </c>
@@ -15336,7 +13506,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="22" customHeight="1">
       <c r="A92" t="n">
         <v>89</v>
       </c>
@@ -15366,7 +13536,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="22" customHeight="1">
       <c r="A93" t="n">
         <v>90</v>
       </c>
@@ -15396,7 +13566,7 @@
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="22" customHeight="1">
       <c r="A94" t="n">
         <v>91</v>
       </c>
@@ -15426,7 +13596,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="22" customHeight="1">
       <c r="A95" t="n">
         <v>92</v>
       </c>
@@ -15456,7 +13626,7 @@
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="22" customHeight="1">
       <c r="A96" t="n">
         <v>93</v>
       </c>
@@ -15486,7 +13656,7 @@
         </is>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="22" customHeight="1">
       <c r="A97" t="n">
         <v>94</v>
       </c>
@@ -15516,7 +13686,7 @@
         </is>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="22" customHeight="1">
       <c r="A98" t="n">
         <v>95</v>
       </c>
@@ -15546,7 +13716,7 @@
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="22" customHeight="1">
       <c r="A99" t="n">
         <v>96</v>
       </c>
@@ -15576,7 +13746,7 @@
         </is>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="22" customHeight="1">
       <c r="A100" t="n">
         <v>97</v>
       </c>
@@ -15606,7 +13776,7 @@
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="22" customHeight="1">
       <c r="A101" t="n">
         <v>98</v>
       </c>
@@ -15636,7 +13806,7 @@
         </is>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="22" customHeight="1">
       <c r="A102" t="n">
         <v>99</v>
       </c>
@@ -15666,7 +13836,7 @@
         </is>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="22" customHeight="1">
       <c r="A103" t="n">
         <v>100</v>
       </c>
@@ -15710,169 +13880,175 @@
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>MAPEAMENTO DISTRITAL E CONGREGAÇÕES (TOTAL 330) - MCASD 2026</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="15" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>Desenvolvido por Valentino Canguele - Huambo, Bié, Cubango, Quando</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Nome da Igreja / Congregação</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Distrito</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>Município</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>Província</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>Delegado Responsável</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>Data do Congresso</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Central Huambo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Distrito Centro</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Huambo</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Huambo</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Huambo</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Huambo</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>Tyindongo Ndjimbo</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>11-13-SET</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Lossambo</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Distrito Centro</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Huambo</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Huambo</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Huambo</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>Huambo</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>Rodrigues Kambanji</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>11-13-SET</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Novo Templo</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Distrito Centro</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Huambo</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Huambo</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Huambo</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>Huambo</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>Enoque Paulino</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>11-13-SET</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>004</t>
@@ -15909,7 +14085,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>005</t>
@@ -15946,7 +14122,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>006</t>
@@ -15983,7 +14159,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>007</t>
@@ -16020,7 +14196,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>008</t>
@@ -16057,7 +14233,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>009</t>
@@ -16094,7 +14270,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>010</t>
@@ -16131,7 +14307,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>011</t>
@@ -16168,7 +14344,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
           <t>012</t>
@@ -16205,7 +14381,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>013</t>
@@ -16242,7 +14418,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>014</t>
@@ -16279,7 +14455,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="22" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
           <t>015</t>
@@ -16316,7 +14492,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="22" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
           <t>016</t>
@@ -16353,7 +14529,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="22" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
           <t>017</t>
@@ -16390,7 +14566,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="22" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
           <t>018</t>
@@ -16427,7 +14603,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="22" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>019</t>
@@ -16464,7 +14640,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="22" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>020</t>
@@ -16501,7 +14677,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="22" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
           <t>080</t>
@@ -16538,7 +14714,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="22" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>081</t>
@@ -16575,7 +14751,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="22" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>082</t>
@@ -16612,7 +14788,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="22" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>083</t>
@@ -16649,7 +14825,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="22" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>250</t>
@@ -16686,7 +14862,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
           <t>251</t>
@@ -16723,7 +14899,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="22" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
           <t>252</t>
@@ -16760,7 +14936,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="22" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
           <t>274</t>
@@ -16797,7 +14973,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="22" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
           <t>281</t>
@@ -16834,7 +15010,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="22" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
           <t>317</t>
@@ -16871,7 +15047,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="22" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
           <t>326</t>
@@ -16922,103 +15098,106 @@
   <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>MATRIZ PARAMÉTRICA DOS 51 CRITÉRIOS DE AVALIAÇÃO PASTORAL</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" s="15" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>Estrutura de Avaliação Desenvolvida por Valentino Canguele</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Área / Categoria</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Item Nº</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Nome do Critério</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>Descrição &amp; Parâmetro de Avaliação</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Assistência Pastoral</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Pontualidade nos Cultos e Reuniões</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Chegada antecipada e cumprimento rigoroso dos horários previstos.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Assistência Pastoral</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Visitação</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>Visita regular aos membros, enfermos, desanimados e novas famílias.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Assistência Pastoral</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Aconselhamento</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Orientação espiritual, ética e prudente a membros e famílias.</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>Assistência Pastoral</t>
@@ -17038,7 +15217,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>Assistência Pastoral</t>
@@ -17058,7 +15237,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>Assistência Pastoral</t>
@@ -17078,7 +15257,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>Assistência Pastoral</t>
@@ -17098,7 +15277,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>Assistência Pastoral</t>
@@ -17118,7 +15297,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>Assistência Pastoral</t>
@@ -17138,7 +15317,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>Assistência Pastoral</t>
@@ -17158,7 +15337,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>Assistência Pastoral</t>
@@ -17178,7 +15357,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
           <t>Relacionamento Pessoal</t>
@@ -17198,7 +15377,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>Relacionamento Pessoal</t>
@@ -17218,7 +15397,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>Relacionamento Pessoal</t>
@@ -17238,7 +15417,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="22" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
           <t>Relacionamento Pessoal</t>
@@ -17258,7 +15437,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="22" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
           <t>Relacionamento Pessoal</t>
@@ -17278,7 +15457,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="22" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
           <t>Relacionamento Pessoal</t>
@@ -17298,7 +15477,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="22" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
           <t>Relacionamento Pessoal</t>
@@ -17318,7 +15497,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="22" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>Relacionamento Pessoal</t>
@@ -17338,7 +15517,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="22" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>Relacionamento Pessoal</t>
@@ -17358,7 +15537,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="22" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
           <t>Relacionamento Pessoal</t>
@@ -17378,7 +15557,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="22" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>Relacionamento Pessoal</t>
@@ -17398,7 +15577,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="22" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>Família Pastoral</t>
@@ -17418,7 +15597,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="22" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>Família Pastoral</t>
@@ -17438,7 +15617,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="22" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>Família Pastoral</t>
@@ -17458,7 +15637,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
           <t>Família Pastoral</t>
@@ -17478,7 +15657,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="22" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
           <t>Família Pastoral</t>
@@ -17498,7 +15677,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="22" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
           <t>Sermões</t>
@@ -17518,7 +15697,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="22" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
           <t>Sermões</t>
@@ -17538,7 +15717,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="22" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
           <t>Sermões</t>
@@ -17558,7 +15737,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="22" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
           <t>Sermões</t>
@@ -17578,7 +15757,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="22" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
           <t>Sermões</t>
@@ -17598,7 +15777,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="22" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
           <t>Sermões</t>
@@ -17618,7 +15797,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="22" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
           <t>Sermões</t>
@@ -17638,7 +15817,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="22" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
           <t>Sermões</t>
@@ -17658,7 +15837,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="22" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17678,7 +15857,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="22" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17698,7 +15877,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="22" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17718,7 +15897,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="22" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17738,7 +15917,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="22" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17758,7 +15937,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="22" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17778,7 +15957,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="22" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17798,7 +15977,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="22" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17818,7 +15997,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="22" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17838,7 +16017,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="22" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17858,7 +16037,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="22" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17878,7 +16057,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="22" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17898,7 +16077,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="22" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17918,7 +16097,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="22" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17938,7 +16117,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="22" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
           <t>Administração</t>
@@ -17958,7 +16137,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="22" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
           <t>Administração</t>
